--- a/grepxcel/examples/02_product_catalog/pattern.xlsx
+++ b/grepxcel/examples/02_product_catalog/pattern.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="34">
   <si>
     <t xml:space="preserve">config:</t>
   </si>
@@ -37,6 +37,18 @@
     <t xml:space="preserve">LR</t>
   </si>
   <si>
+    <t xml:space="preserve">ignore.case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trim.whitespace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yes</t>
+  </si>
+  <si>
     <t xml:space="preserve">lbl:</t>
   </si>
   <si>
@@ -70,19 +82,85 @@
     <t xml:space="preserve">var:</t>
   </si>
   <si>
+    <t xml:space="preserve">catalog.product</t>
+  </si>
+  <si>
     <t xml:space="preserve">.+</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">catalog.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">sku</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">[A-Z]+\d+</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">catalog.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">qty</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">integer</t>
   </si>
   <si>
     <t xml:space="preserve">\d+</t>
   </si>
   <si>
-    <t xml:space="preserve">number</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">catalog.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">price</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">currency</t>
   </si>
   <si>
     <t xml:space="preserve">START:</t>
@@ -94,7 +172,7 @@
     <t xml:space="preserve">HEADER:1</t>
   </si>
   <si>
-    <t xml:space="preserve">DATA:3</t>
+    <t xml:space="preserve">DATA:{1,5}</t>
   </si>
   <si>
     <t xml:space="preserve">END:</t>
@@ -107,7 +185,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -129,6 +207,12 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -203,28 +287,36 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -483,232 +575,275 @@
   <dimension ref="A1:F1048576"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>12</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
+      <c r="A6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
       <c r="C8" s="3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="A10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3" t="s">
+      <c r="E17" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-    </row>
+      <c r="F17" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+    </row>
+    <row r="1048550" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048551" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048552" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
